--- a/Documentos/Documentos Excel - Hojas de calculo/Operadores condicionales y logicos.xlsx
+++ b/Documentos/Documentos Excel - Hojas de calculo/Operadores condicionales y logicos.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\La pagina web de Hernan\Documentos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\La pagina web de Hernan\Documentos\Documentos Excel - Hojas de calculo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628F9B4A-CA37-4C4D-8F7F-6AA0B0863BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0B741E66-5315-4F2F-A9A8-5A64DA5A10D8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -106,7 +105,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -250,6 +249,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -262,11 +263,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Bueno" xfId="1" builtinId="26"/>
+    <cellStyle name="Buena" xfId="1" builtinId="26"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -290,20 +289,20 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="Rectángulo 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D045E7B4-A5A5-BC99-0DDF-EF96B8DC3A3D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D045E7B4-A5A5-BC99-0DDF-EF96B8DC3A3D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -311,8 +310,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5248275" y="190500"/>
-          <a:ext cx="5657850" cy="1476375"/>
+          <a:off x="5248275" y="190501"/>
+          <a:ext cx="5657850" cy="1085850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -386,17 +385,6 @@
             <a:rPr lang="es-AR" sz="1100" baseline="0"/>
             <a:t> que compara un valor determinado, ya sea de tipo numérico o alfabético. Dicho valor nos brinda 2 resultados: uno para verdadero y otro para falso. </a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="es-AR" sz="1100"/>
-            <a:t>En este ejemplo del condicional SI, tenemos que averiguar</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-AR" sz="1100" baseline="0"/>
-            <a:t> si el alumno tiene un promedio mayor o igual a 7 para aprobar "X" materia. Si se cumple dicha condición, aprueba. Caso contrario, desaprueba.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="es-AR" sz="1100" baseline="0"/>
-          </a:br>
           <a:endParaRPr lang="es-AR" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -413,15 +401,15 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="Rectángulo 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BB9FDAE-CEC5-49C4-AB6F-BB0551D2A04A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0BB9FDAE-CEC5-49C4-AB6F-BB0551D2A04A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -430,7 +418,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5191126" y="1885949"/>
-          <a:ext cx="5934074" cy="1676401"/>
+          <a:ext cx="5934074" cy="1466851"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -620,14 +608,6 @@
               </a:solidFill>
             </a:rPr>
           </a:br>
-          <a:r>
-            <a:rPr lang="es-AR" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Este método de calificación de notas se utilizaba anteriormente hasta hace unos cuantos años atrás.</a:t>
-          </a:r>
           <a:endParaRPr lang="es-AR" sz="1100">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
@@ -643,20 +623,20 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>76201</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>38101</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="5" name="Rectángulo 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62D247E9-4422-49DE-8B1B-598888855A91}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{62D247E9-4422-49DE-8B1B-598888855A91}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -664,8 +644,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2571750" y="3695700"/>
-          <a:ext cx="9515476" cy="1495425"/>
+          <a:off x="2571750" y="3695701"/>
+          <a:ext cx="9515476" cy="1028700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -742,34 +722,15 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="es-AR" sz="1100"/>
-            <a:t>Además</a:t>
+            <a:t>En el operador logico </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="es-AR" sz="1100" baseline="0"/>
-            <a:t> del </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-AR" sz="1100"/>
-            <a:t>operador lógico</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-AR" sz="1100" baseline="0"/>
-            <a:t> Y, está O. La diferencia está en que el resultado va a ser verdadero cuando se cumpla una de las condiciones a comparar, mismo caso si llegan a cumplirse las 2. Para que sea falso, no debe cumplirse ninguno.</a:t>
+            <a:t>0 el resultado va a ser verdadero cuando se cumpla una de las condiciones a comparar, mismo caso si llegan a cumplirse las 2. Para que sea falso, no debe cumplirse ninguno.</a:t>
           </a:r>
           <a:br>
             <a:rPr lang="es-AR" sz="1100" baseline="0"/>
           </a:br>
-          <a:r>
-            <a:rPr lang="es-AR" sz="1100" baseline="0"/>
-            <a:t>En este caso, la condición es que los números ingresados en la columna de "Numero 1" sean menores o iguales que 15 "O" que sean mayores o iguales que 60 en la columna de "Número 2".</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="es-AR" sz="1100" baseline="0"/>
-          </a:br>
-          <a:r>
-            <a:rPr lang="es-AR" sz="1100" baseline="0"/>
-            <a:t>Están los 4 escenarios presentados: fila 23, las 2 condiciones se cumplen; fila 24, se cumple la primera; fila 25, se cumple la segunda y fila 26, no se cumple ninguna.</a:t>
-          </a:r>
           <a:endParaRPr lang="es-AR" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -794,7 +755,7 @@
         <xdr:cNvPr id="8" name="CuadroTexto 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55D5810A-F595-608E-CC8B-BEB6E247D536}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{55D5810A-F595-608E-CC8B-BEB6E247D536}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1329,7 +1290,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89A7C93A-A596-4BA1-B414-E785C7697ADA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1339,14 +1300,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1465,32 +1426,32 @@
       <c r="F8" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1591,11 +1552,11 @@
       <c r="F18" s="1"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
@@ -1645,20 +1606,20 @@
       <c r="C26" s="1"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="4" t="s">
         <v>18</v>
       </c>
     </row>
